--- a/practice/answers/q025.xlsx
+++ b/practice/answers/q025.xlsx
@@ -3465,7 +3465,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>(d) On these statistics Brandon is the riskier yielder relative to its average (CV 0.19 vs 0.16), while Manness both yields more (72.1 vs 59.6) and varies less around its mean. One caution belongs in the answer: Manness's numbers rest on far fewer results (108 vs 519), so its statistics are less firmly estimated.</t>

--- a/practice/answers/q025.xlsx
+++ b/practice/answers/q025.xlsx
@@ -3468,7 +3468,7 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>(d) On these statistics Brandon is the riskier yielder relative to its average (CV 0.19 vs 0.16), while Manness both yields more (72.1 vs 59.6) and varies less around its mean. One caution belongs in the answer: Manness's numbers rest on far fewer results (108 vs 519), so its statistics are less firmly estimated.</t>
+          <t>(d) On these statistics Brandon is the riskier choice relative to its average: the two spreads are similar in bushels (sd 11.5 vs 11.1), but Brandon's sits on a much lower mean, so its CV is higher (0.19 vs 0.16) while Manness also simply yields more (72.1 vs 59.6). One caution belongs in the answer: Manness rests on far fewer results (108 vs 519), so its statistics are less firmly estimated.</t>
         </is>
       </c>
     </row>
